--- a/#BillsMafia_anonymized.xlsx
+++ b/#BillsMafia_anonymized.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>关注的userName</t>
+          <t>followed_userName</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>粉丝的userName</t>
+          <t>follower_userName</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>发文量</t>
+          <t>Number of Publications</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -483,12 +483,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>user_00166</t>
+          <t>user_00170</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>user_00168</t>
+          <t>user_00172</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -499,7 +499,7 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>user_00284</t>
+          <t>user_00291</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -526,12 +526,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>user_00166</t>
+          <t>user_00170</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>user_00168</t>
+          <t>user_00172</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -542,7 +542,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>user_00284</t>
+          <t>user_00291</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -570,12 +570,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>user_00166</t>
+          <t>user_00170</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>user_00168</t>
+          <t>user_00172</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,7 +586,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>user_00284</t>
+          <t>user_00291</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -614,12 +614,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>user_00166</t>
+          <t>user_00170</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>user_00168</t>
+          <t>user_00172</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -630,7 +630,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>user_00284</t>
+          <t>user_00291</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -656,12 +656,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>user_00166</t>
+          <t>user_00170</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>user_00168</t>
+          <t>user_00172</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -672,7 +672,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>user_00284</t>
+          <t>user_00291</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -698,12 +698,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>user_00166</t>
+          <t>user_00170</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>user_00168</t>
+          <t>user_00172</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -714,7 +714,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>user_00284</t>
+          <t>user_00291</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -740,12 +740,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>user_00166</t>
+          <t>user_00170</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>user_00168</t>
+          <t>user_00172</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -756,7 +756,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>user_00284</t>
+          <t>user_00291</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -782,12 +782,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>user_01335</t>
+          <t>user_01355</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>user_01334</t>
+          <t>user_01354</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -798,7 +798,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>user_00168</t>
+          <t>user_00172</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -822,12 +822,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>user_01335</t>
+          <t>user_01355</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>user_01334</t>
+          <t>user_01354</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -854,12 +854,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>user_01335</t>
+          <t>user_01355</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>user_01334</t>
+          <t>user_01354</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -886,12 +886,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>user_01335</t>
+          <t>user_01355</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>user_01334</t>
+          <t>user_01354</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -918,12 +918,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>user_01335</t>
+          <t>user_01355</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>user_01334</t>
+          <t>user_01354</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -950,12 +950,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>user_01335</t>
+          <t>user_01355</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>user_01334</t>
+          <t>user_01354</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -982,12 +982,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>user_01335</t>
+          <t>user_01355</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>user_01334</t>
+          <t>user_01354</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1014,12 +1014,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>user_01335</t>
+          <t>user_01355</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>user_01334</t>
+          <t>user_01354</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1046,12 +1046,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>user_01335</t>
+          <t>user_01355</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>user_01334</t>
+          <t>user_01354</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1078,12 +1078,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>user_01335</t>
+          <t>user_01355</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>user_01334</t>
+          <t>user_01354</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1110,12 +1110,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>user_01335</t>
+          <t>user_01355</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>user_01334</t>
+          <t>user_01354</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1142,12 +1142,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>user_01335</t>
+          <t>user_01355</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>user_01334</t>
+          <t>user_01354</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1176,12 +1176,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>user_01335</t>
+          <t>user_01355</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>user_01334</t>
+          <t>user_01354</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1208,12 +1208,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>user_01335</t>
+          <t>user_01355</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>user_01334</t>
+          <t>user_01354</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1240,12 +1240,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>user_01335</t>
+          <t>user_01355</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>user_01334</t>
+          <t>user_01354</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1275,12 +1275,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>user_01335</t>
+          <t>user_01355</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>user_01334</t>
+          <t>user_01354</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1309,12 +1309,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>user_01335</t>
+          <t>user_01355</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>user_01334</t>
+          <t>user_01354</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1341,12 +1341,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>user_00529</t>
+          <t>user_00537</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>user_00530</t>
+          <t>user_00538</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1357,7 +1357,7 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>user_00168</t>
+          <t>user_00172</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1379,12 +1379,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>user_01451</t>
+          <t>user_01472</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>user_01451</t>
+          <t>user_01472</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1395,7 +1395,7 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>user_00168</t>
+          <t>user_00172</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1417,12 +1417,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>user_01022</t>
+          <t>user_01036</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>user_01023</t>
+          <t>user_01037</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1433,7 +1433,7 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>user_00168</t>
+          <t>user_00172</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1455,12 +1455,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>user_01331</t>
+          <t>user_01351</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>user_01333</t>
+          <t>user_01353</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1471,7 +1471,7 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>user_00168</t>
+          <t>user_00172</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1493,12 +1493,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>user_01331</t>
+          <t>user_01351</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>user_01333</t>
+          <t>user_01353</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1526,12 +1526,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>user_01331</t>
+          <t>user_01351</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>user_01333</t>
+          <t>user_01353</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1558,12 +1558,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>user_01331</t>
+          <t>user_01351</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>user_01333</t>
+          <t>user_01353</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1590,12 +1590,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>user_01331</t>
+          <t>user_01351</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>user_01333</t>
+          <t>user_01353</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1622,12 +1622,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>user_01331</t>
+          <t>user_01351</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>user_01333</t>
+          <t>user_01353</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1655,12 +1655,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>user_01331</t>
+          <t>user_01351</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>user_01333</t>
+          <t>user_01353</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1687,12 +1687,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>user_01331</t>
+          <t>user_01351</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>user_01333</t>
+          <t>user_01353</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1719,12 +1719,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>user_01331</t>
+          <t>user_01351</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>user_01333</t>
+          <t>user_01353</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1753,12 +1753,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>user_01331</t>
+          <t>user_01351</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>user_01333</t>
+          <t>user_01353</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1787,12 +1787,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>user_01331</t>
+          <t>user_01351</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>user_01333</t>
+          <t>user_01353</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1820,12 +1820,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>user_01331</t>
+          <t>user_01351</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>user_01333</t>
+          <t>user_01353</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1853,12 +1853,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>user_01331</t>
+          <t>user_01351</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>user_01333</t>
+          <t>user_01353</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1886,12 +1886,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>user_01331</t>
+          <t>user_01351</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>user_01333</t>
+          <t>user_01353</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1919,12 +1919,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>user_01331</t>
+          <t>user_01351</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>user_01333</t>
+          <t>user_01353</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1951,12 +1951,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>user_01331</t>
+          <t>user_01351</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>user_01333</t>
+          <t>user_01353</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1984,12 +1984,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>user_01331</t>
+          <t>user_01351</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>user_01333</t>
+          <t>user_01353</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2016,12 +2016,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>user_01331</t>
+          <t>user_01351</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>user_01333</t>
+          <t>user_01353</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2048,12 +2048,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>user_01331</t>
+          <t>user_01351</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>user_01333</t>
+          <t>user_01353</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2080,12 +2080,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>user_01331</t>
+          <t>user_01351</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>user_01333</t>
+          <t>user_01353</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2113,12 +2113,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>user_01331</t>
+          <t>user_01351</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>user_01333</t>
+          <t>user_01353</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2145,12 +2145,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>user_00893</t>
+          <t>user_00906</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>user_02416</t>
+          <t>user_02460</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2161,7 +2161,7 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>user_00168</t>
+          <t>user_00172</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2183,12 +2183,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>user_00893</t>
+          <t>user_00906</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>user_02416</t>
+          <t>user_02460</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2216,12 +2216,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>user_00893</t>
+          <t>user_00906</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>user_02416</t>
+          <t>user_02460</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2248,12 +2248,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>user_00893</t>
+          <t>user_00906</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>user_02416</t>
+          <t>user_02460</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2281,12 +2281,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>user_00893</t>
+          <t>user_00906</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>user_02416</t>
+          <t>user_02460</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2313,12 +2313,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>user_00893</t>
+          <t>user_00906</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>user_02416</t>
+          <t>user_02460</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2347,12 +2347,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>user_00893</t>
+          <t>user_00906</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>user_02416</t>
+          <t>user_02460</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2379,12 +2379,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>user_00893</t>
+          <t>user_00906</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>user_02416</t>
+          <t>user_02460</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2418,12 +2418,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>user_00893</t>
+          <t>user_00906</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>user_02416</t>
+          <t>user_02460</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2455,12 +2455,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>user_00893</t>
+          <t>user_00906</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>user_02416</t>
+          <t>user_02460</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2492,12 +2492,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>user_00893</t>
+          <t>user_00906</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>user_02416</t>
+          <t>user_02460</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2527,12 +2527,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>user_00893</t>
+          <t>user_00906</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>user_02416</t>
+          <t>user_02460</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2559,12 +2559,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>user_00893</t>
+          <t>user_00906</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>user_02416</t>
+          <t>user_02460</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2591,12 +2591,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>user_00893</t>
+          <t>user_00906</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>user_02416</t>
+          <t>user_02460</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2623,12 +2623,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>user_00893</t>
+          <t>user_00906</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>user_02416</t>
+          <t>user_02460</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2655,12 +2655,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>user_00893</t>
+          <t>user_00906</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>user_02416</t>
+          <t>user_02460</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2689,12 +2689,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>user_00893</t>
+          <t>user_00906</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>user_02416</t>
+          <t>user_02460</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2721,12 +2721,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>user_00893</t>
+          <t>user_00906</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>user_02416</t>
+          <t>user_02460</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2756,12 +2756,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>user_00893</t>
+          <t>user_00906</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>user_02416</t>
+          <t>user_02460</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2789,12 +2789,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>user_00893</t>
+          <t>user_00906</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>user_02416</t>
+          <t>user_02460</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2821,12 +2821,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>user_00893</t>
+          <t>user_00906</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>user_02416</t>
+          <t>user_02460</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2853,12 +2853,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>user_01044</t>
+          <t>user_01059</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>user_01045</t>
+          <t>user_01060</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2869,7 +2869,7 @@
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>user_00168</t>
+          <t>user_00172</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2892,12 +2892,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>user_01035</t>
+          <t>user_01049</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>user_01037</t>
+          <t>user_01051</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2908,7 +2908,7 @@
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>user_00168</t>
+          <t>user_00172</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2930,12 +2930,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>user_01035</t>
+          <t>user_01049</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>user_01037</t>
+          <t>user_01051</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2962,12 +2962,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>user_01035</t>
+          <t>user_01049</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>user_01037</t>
+          <t>user_01051</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2994,12 +2994,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>user_01035</t>
+          <t>user_01049</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>user_01037</t>
+          <t>user_01051</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3028,12 +3028,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>user_01035</t>
+          <t>user_01049</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>user_01037</t>
+          <t>user_01051</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>user_01035</t>
+          <t>user_01049</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>user_01037</t>
+          <t>user_01051</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3093,12 +3093,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>user_01035</t>
+          <t>user_01049</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>user_01037</t>
+          <t>user_01051</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3125,12 +3125,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>user_01035</t>
+          <t>user_01049</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>user_01037</t>
+          <t>user_01051</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3157,12 +3157,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>user_01035</t>
+          <t>user_01049</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>user_01037</t>
+          <t>user_01051</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3189,12 +3189,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>user_01035</t>
+          <t>user_01049</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>user_01037</t>
+          <t>user_01051</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3221,12 +3221,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>user_01035</t>
+          <t>user_01049</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>user_01037</t>
+          <t>user_01051</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3253,12 +3253,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>user_01035</t>
+          <t>user_01049</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>user_01037</t>
+          <t>user_01051</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3285,12 +3285,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>user_01035</t>
+          <t>user_01049</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>user_01037</t>
+          <t>user_01051</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3317,12 +3317,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>user_01035</t>
+          <t>user_01049</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>user_01037</t>
+          <t>user_01051</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3349,12 +3349,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>user_01035</t>
+          <t>user_01049</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>user_01037</t>
+          <t>user_01051</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3381,12 +3381,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>user_01035</t>
+          <t>user_01049</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>user_01037</t>
+          <t>user_01051</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3420,12 +3420,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>user_01035</t>
+          <t>user_01049</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>user_01037</t>
+          <t>user_01051</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3462,12 +3462,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>user_01035</t>
+          <t>user_01049</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>user_01037</t>
+          <t>user_01051</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3501,12 +3501,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>user_01035</t>
+          <t>user_01049</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>user_01037</t>
+          <t>user_01051</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3533,12 +3533,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>user_01035</t>
+          <t>user_01049</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>user_01037</t>
+          <t>user_01051</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3565,12 +3565,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>user_01035</t>
+          <t>user_01049</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>user_01037</t>
+          <t>user_01051</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3597,12 +3597,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>user_01035</t>
+          <t>user_01049</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>user_01037</t>
+          <t>user_01051</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3633,12 +3633,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>user_00842</t>
+          <t>user_00855</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>user_00844</t>
+          <t>user_00857</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3649,7 +3649,7 @@
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>user_00168</t>
+          <t>user_00172</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -3672,12 +3672,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>user_00842</t>
+          <t>user_00855</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>user_00844</t>
+          <t>user_00857</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3705,12 +3705,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>user_00842</t>
+          <t>user_00855</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>user_00844</t>
+          <t>user_00857</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3737,12 +3737,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>user_00842</t>
+          <t>user_00855</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>user_00844</t>
+          <t>user_00857</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3769,12 +3769,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>user_00842</t>
+          <t>user_00855</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>user_00844</t>
+          <t>user_00857</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3801,12 +3801,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>user_00842</t>
+          <t>user_00855</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>user_00844</t>
+          <t>user_00857</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3833,12 +3833,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>user_00842</t>
+          <t>user_00855</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>user_00844</t>
+          <t>user_00857</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3865,12 +3865,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>user_00842</t>
+          <t>user_00855</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>user_00844</t>
+          <t>user_00857</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3900,12 +3900,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>user_00842</t>
+          <t>user_00855</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>user_00844</t>
+          <t>user_00857</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3936,12 +3936,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>user_00842</t>
+          <t>user_00855</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>user_00844</t>
+          <t>user_00857</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3968,12 +3968,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>user_00842</t>
+          <t>user_00855</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>user_00844</t>
+          <t>user_00857</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4000,12 +4000,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>user_00842</t>
+          <t>user_00855</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>user_00844</t>
+          <t>user_00857</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4033,12 +4033,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>user_00842</t>
+          <t>user_00855</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>user_00844</t>
+          <t>user_00857</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4065,12 +4065,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>user_00842</t>
+          <t>user_00855</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>user_00844</t>
+          <t>user_00857</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4099,12 +4099,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>user_00842</t>
+          <t>user_00855</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>user_00844</t>
+          <t>user_00857</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4131,12 +4131,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>user_00842</t>
+          <t>user_00855</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>user_00844</t>
+          <t>user_00857</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4165,12 +4165,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>user_00842</t>
+          <t>user_00855</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>user_00844</t>
+          <t>user_00857</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4197,12 +4197,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>user_00842</t>
+          <t>user_00855</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>user_00844</t>
+          <t>user_00857</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4229,12 +4229,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>user_00842</t>
+          <t>user_00855</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>user_00844</t>
+          <t>user_00857</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4262,12 +4262,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>user_00842</t>
+          <t>user_00855</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>user_00844</t>
+          <t>user_00857</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4294,12 +4294,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>user_02112</t>
+          <t>user_02136</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>user_02113</t>
+          <t>user_02137</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4310,7 +4310,7 @@
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>user_00168</t>
+          <t>user_00172</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -4334,12 +4334,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>user_02112</t>
+          <t>user_02136</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>user_02113</t>
+          <t>user_02137</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4366,12 +4366,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>user_02112</t>
+          <t>user_02136</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>user_02113</t>
+          <t>user_02137</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4402,12 +4402,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>user_02112</t>
+          <t>user_02136</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>user_02113</t>
+          <t>user_02137</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4437,12 +4437,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>user_02112</t>
+          <t>user_02136</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>user_02113</t>
+          <t>user_02137</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4469,12 +4469,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>user_02112</t>
+          <t>user_02136</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>user_02113</t>
+          <t>user_02137</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4502,12 +4502,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>user_02112</t>
+          <t>user_02136</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>user_02113</t>
+          <t>user_02137</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4536,12 +4536,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>user_02112</t>
+          <t>user_02136</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>user_02113</t>
+          <t>user_02137</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4568,12 +4568,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>user_02112</t>
+          <t>user_02136</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>user_02113</t>
+          <t>user_02137</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4600,12 +4600,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>user_02112</t>
+          <t>user_02136</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>user_02113</t>
+          <t>user_02137</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4633,12 +4633,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>user_02112</t>
+          <t>user_02136</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>user_02113</t>
+          <t>user_02137</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4667,12 +4667,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>user_02112</t>
+          <t>user_02136</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>user_02113</t>
+          <t>user_02137</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4699,12 +4699,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>user_02112</t>
+          <t>user_02136</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>user_02113</t>
+          <t>user_02137</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4731,12 +4731,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>user_02112</t>
+          <t>user_02136</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>user_02113</t>
+          <t>user_02137</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4763,12 +4763,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>user_02112</t>
+          <t>user_02136</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>user_02113</t>
+          <t>user_02137</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4795,12 +4795,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>user_02112</t>
+          <t>user_02136</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>user_02113</t>
+          <t>user_02137</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4827,12 +4827,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>user_02112</t>
+          <t>user_02136</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>user_02113</t>
+          <t>user_02137</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4860,12 +4860,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>user_02112</t>
+          <t>user_02136</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>user_02113</t>
+          <t>user_02137</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4893,12 +4893,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>user_02112</t>
+          <t>user_02136</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>user_02113</t>
+          <t>user_02137</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4925,12 +4925,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>user_02112</t>
+          <t>user_02136</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>user_02113</t>
+          <t>user_02137</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4957,12 +4957,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>user_02112</t>
+          <t>user_02136</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>user_02113</t>
+          <t>user_02137</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4990,12 +4990,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>user_00283</t>
+          <t>user_00290</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>user_00284</t>
+          <t>user_00291</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5006,7 +5006,7 @@
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -5033,12 +5033,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>user_00283</t>
+          <t>user_00290</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>user_00284</t>
+          <t>user_00291</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5049,7 +5049,7 @@
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="F136" t="n">
@@ -5076,12 +5076,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>user_00283</t>
+          <t>user_00290</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>user_00284</t>
+          <t>user_00291</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5092,7 +5092,7 @@
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="F137" t="n">
@@ -5119,12 +5119,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>user_00283</t>
+          <t>user_00290</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>user_00284</t>
+          <t>user_00291</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5135,7 +5135,7 @@
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="F138" t="n">
@@ -5162,12 +5162,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>user_00283</t>
+          <t>user_00290</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>user_00284</t>
+          <t>user_00291</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5178,7 +5178,7 @@
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="F139" t="n">
@@ -5205,12 +5205,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>user_00283</t>
+          <t>user_00290</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>user_00284</t>
+          <t>user_00291</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5221,7 +5221,7 @@
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="F140" t="n">
@@ -5249,12 +5249,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>user_00283</t>
+          <t>user_00290</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>user_00284</t>
+          <t>user_00291</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5265,7 +5265,7 @@
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -5300,12 +5300,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>user_00551</t>
+          <t>user_00559</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
@@ -5342,12 +5342,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>user_00551</t>
+          <t>user_00559</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -5385,12 +5385,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>user_00551</t>
+          <t>user_00559</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -5429,12 +5429,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>user_00551</t>
+          <t>user_00559</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -5472,12 +5472,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>user_00551</t>
+          <t>user_00559</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -5515,12 +5515,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>user_00551</t>
+          <t>user_00559</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -5559,12 +5559,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>user_00551</t>
+          <t>user_00559</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -5602,12 +5602,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>user_00551</t>
+          <t>user_00559</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5635,12 +5635,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>user_00551</t>
+          <t>user_00559</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5667,12 +5667,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>user_00551</t>
+          <t>user_00559</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5699,12 +5699,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>user_00551</t>
+          <t>user_00559</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5731,12 +5731,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>user_00551</t>
+          <t>user_00559</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5763,12 +5763,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>user_00551</t>
+          <t>user_00559</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5795,12 +5795,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>user_00551</t>
+          <t>user_00559</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5827,12 +5827,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>user_00551</t>
+          <t>user_00559</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5859,12 +5859,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>user_00551</t>
+          <t>user_00559</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5894,12 +5894,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>user_00551</t>
+          <t>user_00559</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5926,12 +5926,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>user_00551</t>
+          <t>user_00559</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5959,12 +5959,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>user_00551</t>
+          <t>user_00559</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5992,12 +5992,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>user_00551</t>
+          <t>user_00559</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6024,12 +6024,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>user_00551</t>
+          <t>user_00559</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6057,12 +6057,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>user_00551</t>
+          <t>user_00559</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6090,12 +6090,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>user_00551</t>
+          <t>user_00559</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6122,12 +6122,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>user_00551</t>
+          <t>user_00559</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6154,12 +6154,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>user_00551</t>
+          <t>user_00559</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6186,12 +6186,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>user_00551</t>
+          <t>user_00559</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6219,12 +6219,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>user_00551</t>
+          <t>user_00559</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6252,12 +6252,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>user_00177</t>
+          <t>user_00181</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>user_00179</t>
+          <t>user_00183</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6268,7 +6268,7 @@
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>user_00486</t>
+          <t>user_00494</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -6290,12 +6290,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>user_00786</t>
+          <t>user_00799</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -6332,12 +6332,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>user_00786</t>
+          <t>user_00799</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -6379,12 +6379,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>user_00786</t>
+          <t>user_00799</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -6421,12 +6421,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>user_00786</t>
+          <t>user_00799</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -6463,12 +6463,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>user_00786</t>
+          <t>user_00799</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -6505,12 +6505,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>user_00786</t>
+          <t>user_00799</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6520,7 +6520,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -6547,12 +6547,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>user_00786</t>
+          <t>user_00799</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -6589,12 +6589,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>user_00786</t>
+          <t>user_00799</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6622,12 +6622,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>user_00786</t>
+          <t>user_00799</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6655,12 +6655,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>user_00786</t>
+          <t>user_00799</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6688,12 +6688,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>user_00786</t>
+          <t>user_00799</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6722,12 +6722,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>user_00786</t>
+          <t>user_00799</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6755,12 +6755,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>user_00786</t>
+          <t>user_00799</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6793,12 +6793,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>user_00786</t>
+          <t>user_00799</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6828,12 +6828,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>user_00786</t>
+          <t>user_00799</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6861,12 +6861,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>user_00786</t>
+          <t>user_00799</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6895,12 +6895,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>user_00786</t>
+          <t>user_00799</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6928,12 +6928,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>user_00786</t>
+          <t>user_00799</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6961,12 +6961,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>user_00786</t>
+          <t>user_00799</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6994,12 +6994,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>user_00786</t>
+          <t>user_00799</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7028,12 +7028,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>user_00786</t>
+          <t>user_00799</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7060,12 +7060,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>user_00786</t>
+          <t>user_00799</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7093,12 +7093,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>user_00786</t>
+          <t>user_00799</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7130,12 +7130,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>user_00786</t>
+          <t>user_00799</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7162,12 +7162,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>user_00786</t>
+          <t>user_00799</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7194,12 +7194,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>user_00786</t>
+          <t>user_00799</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7226,12 +7226,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>user_00786</t>
+          <t>user_00799</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7258,12 +7258,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>user_02941</t>
+          <t>user_03020</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>user_00856</t>
+          <t>user_00869</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7274,7 +7274,7 @@
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -7296,12 +7296,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>user_02940</t>
+          <t>user_03019</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>user_00856</t>
+          <t>user_00869</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7328,12 +7328,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>user_02940</t>
+          <t>user_03019</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>user_00856</t>
+          <t>user_00869</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7361,12 +7361,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>user_02940</t>
+          <t>user_03019</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>user_00856</t>
+          <t>user_00869</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7393,12 +7393,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>user_02940</t>
+          <t>user_03019</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>user_00856</t>
+          <t>user_00869</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7425,12 +7425,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>user_02940</t>
+          <t>user_03019</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>user_00856</t>
+          <t>user_00869</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7457,12 +7457,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>user_02940</t>
+          <t>user_03019</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>user_00856</t>
+          <t>user_00869</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7501,12 +7501,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>user_02940</t>
+          <t>user_03019</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>user_00856</t>
+          <t>user_00869</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7534,12 +7534,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>user_02940</t>
+          <t>user_03019</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>user_00856</t>
+          <t>user_00869</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7566,12 +7566,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>user_02940</t>
+          <t>user_03019</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>user_00856</t>
+          <t>user_00869</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7598,12 +7598,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>user_02940</t>
+          <t>user_03019</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>user_00856</t>
+          <t>user_00869</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7630,12 +7630,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>user_02940</t>
+          <t>user_03019</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>user_00856</t>
+          <t>user_00869</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7664,12 +7664,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>user_02940</t>
+          <t>user_03019</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>user_00856</t>
+          <t>user_00869</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7700,12 +7700,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>user_02940</t>
+          <t>user_03019</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>user_00856</t>
+          <t>user_00869</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7732,12 +7732,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>user_02940</t>
+          <t>user_03019</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>user_00856</t>
+          <t>user_00869</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7764,12 +7764,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>user_02940</t>
+          <t>user_03019</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>user_00856</t>
+          <t>user_00869</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7797,12 +7797,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>user_02940</t>
+          <t>user_03019</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>user_00856</t>
+          <t>user_00869</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7829,12 +7829,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>user_02940</t>
+          <t>user_03019</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>user_00856</t>
+          <t>user_00869</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7861,12 +7861,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>user_02940</t>
+          <t>user_03019</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>user_00856</t>
+          <t>user_00869</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7893,12 +7893,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>user_02940</t>
+          <t>user_03019</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>user_00856</t>
+          <t>user_00869</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7925,12 +7925,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>user_02940</t>
+          <t>user_03019</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>user_00856</t>
+          <t>user_00869</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -7957,12 +7957,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>user_00619</t>
+          <t>user_00628</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>user_00622</t>
+          <t>user_00631</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -7973,7 +7973,7 @@
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="F218" t="n">
@@ -7997,12 +7997,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>user_01442</t>
+          <t>user_01463</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>user_01443</t>
+          <t>user_01464</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8013,7 +8013,7 @@
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="F219" t="n">
@@ -8035,12 +8035,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>user_01442</t>
+          <t>user_01463</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>user_01443</t>
+          <t>user_01464</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8071,12 +8071,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>user_01442</t>
+          <t>user_01463</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>user_01443</t>
+          <t>user_01464</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8104,12 +8104,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>user_01442</t>
+          <t>user_01463</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>user_01443</t>
+          <t>user_01464</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8137,12 +8137,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>user_01442</t>
+          <t>user_01463</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>user_01443</t>
+          <t>user_01464</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8171,12 +8171,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>user_01442</t>
+          <t>user_01463</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>user_01443</t>
+          <t>user_01464</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8209,12 +8209,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>user_01442</t>
+          <t>user_01463</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>user_01443</t>
+          <t>user_01464</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8242,12 +8242,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>user_01442</t>
+          <t>user_01463</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>user_01443</t>
+          <t>user_01464</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8274,12 +8274,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>user_01442</t>
+          <t>user_01463</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>user_01443</t>
+          <t>user_01464</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8307,12 +8307,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>user_01442</t>
+          <t>user_01463</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>user_01443</t>
+          <t>user_01464</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8339,12 +8339,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>user_01442</t>
+          <t>user_01463</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>user_01443</t>
+          <t>user_01464</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8372,12 +8372,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>user_01442</t>
+          <t>user_01463</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>user_01443</t>
+          <t>user_01464</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8404,12 +8404,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>user_01442</t>
+          <t>user_01463</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>user_01443</t>
+          <t>user_01464</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8436,12 +8436,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>user_01442</t>
+          <t>user_01463</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>user_01443</t>
+          <t>user_01464</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8468,12 +8468,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>user_01442</t>
+          <t>user_01463</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>user_01443</t>
+          <t>user_01464</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8501,12 +8501,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>user_01442</t>
+          <t>user_01463</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>user_01443</t>
+          <t>user_01464</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8533,12 +8533,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>user_01442</t>
+          <t>user_01463</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>user_01443</t>
+          <t>user_01464</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -8569,12 +8569,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>user_01442</t>
+          <t>user_01463</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>user_01443</t>
+          <t>user_01464</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8605,12 +8605,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>user_01442</t>
+          <t>user_01463</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>user_01443</t>
+          <t>user_01464</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8638,12 +8638,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>user_01442</t>
+          <t>user_01463</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>user_01443</t>
+          <t>user_01464</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -8671,12 +8671,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>user_01442</t>
+          <t>user_01463</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>user_01443</t>
+          <t>user_01464</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -8704,12 +8704,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>user_01281</t>
+          <t>user_01301</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>user_01282</t>
+          <t>user_01302</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -8720,7 +8720,7 @@
       <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="F240" t="n">
@@ -8742,12 +8742,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>user_01281</t>
+          <t>user_01301</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>user_01282</t>
+          <t>user_01302</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -8774,12 +8774,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>user_01281</t>
+          <t>user_01301</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>user_01282</t>
+          <t>user_01302</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -8806,12 +8806,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>user_01281</t>
+          <t>user_01301</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>user_01282</t>
+          <t>user_01302</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -8838,12 +8838,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>user_01281</t>
+          <t>user_01301</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>user_01282</t>
+          <t>user_01302</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -8871,12 +8871,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>user_01281</t>
+          <t>user_01301</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>user_01282</t>
+          <t>user_01302</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -8903,12 +8903,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>user_01281</t>
+          <t>user_01301</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>user_01282</t>
+          <t>user_01302</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -8936,12 +8936,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>user_01281</t>
+          <t>user_01301</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>user_01282</t>
+          <t>user_01302</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -8968,12 +8968,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>user_01281</t>
+          <t>user_01301</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>user_01282</t>
+          <t>user_01302</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9000,12 +9000,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>user_01281</t>
+          <t>user_01301</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>user_01282</t>
+          <t>user_01302</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9033,12 +9033,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>user_01281</t>
+          <t>user_01301</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>user_01282</t>
+          <t>user_01302</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9065,12 +9065,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>user_01281</t>
+          <t>user_01301</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>user_01282</t>
+          <t>user_01302</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -9101,12 +9101,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>user_01281</t>
+          <t>user_01301</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>user_01282</t>
+          <t>user_01302</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9133,12 +9133,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>user_01281</t>
+          <t>user_01301</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>user_01282</t>
+          <t>user_01302</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9165,12 +9165,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>user_01281</t>
+          <t>user_01301</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>user_01282</t>
+          <t>user_01302</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9197,12 +9197,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>user_01281</t>
+          <t>user_01301</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>user_01282</t>
+          <t>user_01302</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9229,12 +9229,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>user_01281</t>
+          <t>user_01301</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>user_01282</t>
+          <t>user_01302</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -9261,12 +9261,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>user_01281</t>
+          <t>user_01301</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>user_01282</t>
+          <t>user_01302</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9293,12 +9293,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>user_01281</t>
+          <t>user_01301</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>user_01282</t>
+          <t>user_01302</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9327,12 +9327,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>user_01281</t>
+          <t>user_01301</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>user_01282</t>
+          <t>user_01302</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9361,12 +9361,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>user_01281</t>
+          <t>user_01301</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>user_01282</t>
+          <t>user_01302</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9394,12 +9394,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>user_01010</t>
+          <t>user_01024</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>user_01012</t>
+          <t>user_01026</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9410,7 +9410,7 @@
       <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="F261" t="n">
@@ -9432,12 +9432,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>user_01010</t>
+          <t>user_01024</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>user_01012</t>
+          <t>user_01026</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9465,12 +9465,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>user_01010</t>
+          <t>user_01024</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>user_01012</t>
+          <t>user_01026</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9497,12 +9497,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>user_01010</t>
+          <t>user_01024</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>user_01012</t>
+          <t>user_01026</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -9531,12 +9531,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>user_01010</t>
+          <t>user_01024</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>user_01012</t>
+          <t>user_01026</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -9564,12 +9564,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>user_01010</t>
+          <t>user_01024</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>user_01012</t>
+          <t>user_01026</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -9605,12 +9605,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>user_01010</t>
+          <t>user_01024</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>user_01012</t>
+          <t>user_01026</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -9640,12 +9640,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>user_01010</t>
+          <t>user_01024</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>user_01012</t>
+          <t>user_01026</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -9675,12 +9675,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>user_01010</t>
+          <t>user_01024</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>user_01012</t>
+          <t>user_01026</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -9709,12 +9709,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>user_01010</t>
+          <t>user_01024</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>user_01012</t>
+          <t>user_01026</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -9742,12 +9742,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>user_01010</t>
+          <t>user_01024</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>user_01012</t>
+          <t>user_01026</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -9775,12 +9775,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>user_01010</t>
+          <t>user_01024</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>user_01012</t>
+          <t>user_01026</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -9807,12 +9807,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>user_01010</t>
+          <t>user_01024</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>user_01012</t>
+          <t>user_01026</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -9840,12 +9840,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>user_01010</t>
+          <t>user_01024</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>user_01012</t>
+          <t>user_01026</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -9875,12 +9875,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>user_01010</t>
+          <t>user_01024</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>user_01012</t>
+          <t>user_01026</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -9907,12 +9907,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>user_01010</t>
+          <t>user_01024</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>user_01012</t>
+          <t>user_01026</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -9939,12 +9939,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>user_01010</t>
+          <t>user_01024</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>user_01012</t>
+          <t>user_01026</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -9972,12 +9972,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>user_01010</t>
+          <t>user_01024</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>user_01012</t>
+          <t>user_01026</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -10004,12 +10004,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>user_01010</t>
+          <t>user_01024</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>user_01012</t>
+          <t>user_01026</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -10036,12 +10036,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>user_01010</t>
+          <t>user_01024</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>user_01012</t>
+          <t>user_01026</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -10070,12 +10070,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>user_00381</t>
+          <t>user_00389</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>user_00383</t>
+          <t>user_00391</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -10086,7 +10086,7 @@
       <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -10108,12 +10108,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>user_00259</t>
+          <t>user_00265</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>user_02303</t>
+          <t>user_02337</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -10124,7 +10124,7 @@
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -10146,12 +10146,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>user_00259</t>
+          <t>user_00265</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>user_02303</t>
+          <t>user_02337</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -10182,12 +10182,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>user_00259</t>
+          <t>user_00265</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>user_02303</t>
+          <t>user_02337</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -10214,12 +10214,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>user_00259</t>
+          <t>user_00265</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>user_02303</t>
+          <t>user_02337</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -10246,12 +10246,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>user_00259</t>
+          <t>user_00265</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>user_02303</t>
+          <t>user_02337</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -10278,12 +10278,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>user_00259</t>
+          <t>user_00265</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>user_02303</t>
+          <t>user_02337</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -10310,12 +10310,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>user_00259</t>
+          <t>user_00265</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>user_02303</t>
+          <t>user_02337</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -10344,12 +10344,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>user_00259</t>
+          <t>user_00265</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>user_02303</t>
+          <t>user_02337</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -10376,12 +10376,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>user_00259</t>
+          <t>user_00265</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>user_02303</t>
+          <t>user_02337</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -10408,12 +10408,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>user_00259</t>
+          <t>user_00265</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>user_02303</t>
+          <t>user_02337</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -10440,12 +10440,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>user_00259</t>
+          <t>user_00265</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>user_02303</t>
+          <t>user_02337</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -10473,12 +10473,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>user_00259</t>
+          <t>user_00265</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>user_02303</t>
+          <t>user_02337</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -10505,12 +10505,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>user_00259</t>
+          <t>user_00265</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>user_02303</t>
+          <t>user_02337</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -10537,12 +10537,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>user_00259</t>
+          <t>user_00265</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>user_02303</t>
+          <t>user_02337</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -10569,12 +10569,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>user_00259</t>
+          <t>user_00265</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>user_02303</t>
+          <t>user_02337</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -10602,12 +10602,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>user_00259</t>
+          <t>user_00265</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>user_02303</t>
+          <t>user_02337</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -10635,12 +10635,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>user_00259</t>
+          <t>user_00265</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>user_02303</t>
+          <t>user_02337</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -10667,12 +10667,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>user_00259</t>
+          <t>user_00265</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>user_02303</t>
+          <t>user_02337</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -10699,12 +10699,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>user_00259</t>
+          <t>user_00265</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>user_02303</t>
+          <t>user_02337</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -10731,12 +10731,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>user_00259</t>
+          <t>user_00265</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>user_02303</t>
+          <t>user_02337</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -10763,12 +10763,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>user_00259</t>
+          <t>user_00265</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>user_02303</t>
+          <t>user_02337</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -10796,12 +10796,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>user_00300</t>
+          <t>user_00307</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>user_00278</t>
+          <t>user_00285</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -10812,7 +10812,7 @@
       <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="F303" t="n">
@@ -10834,12 +10834,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>user_00300</t>
+          <t>user_00307</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>user_00278</t>
+          <t>user_00285</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -10866,12 +10866,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>user_00300</t>
+          <t>user_00307</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>user_00278</t>
+          <t>user_00285</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -10905,12 +10905,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>user_00300</t>
+          <t>user_00307</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>user_00278</t>
+          <t>user_00285</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -10940,12 +10940,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>user_00300</t>
+          <t>user_00307</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>user_00278</t>
+          <t>user_00285</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -10972,12 +10972,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>user_00300</t>
+          <t>user_00307</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>user_00278</t>
+          <t>user_00285</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -11005,12 +11005,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>user_00300</t>
+          <t>user_00307</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>user_00278</t>
+          <t>user_00285</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -11039,12 +11039,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>user_00300</t>
+          <t>user_00307</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>user_00278</t>
+          <t>user_00285</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -11072,12 +11072,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>user_00300</t>
+          <t>user_00307</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>user_00278</t>
+          <t>user_00285</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -11104,12 +11104,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>user_00300</t>
+          <t>user_00307</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>user_00278</t>
+          <t>user_00285</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -11136,12 +11136,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>user_00300</t>
+          <t>user_00307</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>user_00278</t>
+          <t>user_00285</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -11168,12 +11168,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>user_00300</t>
+          <t>user_00307</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>user_00278</t>
+          <t>user_00285</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -11200,12 +11200,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>user_00300</t>
+          <t>user_00307</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>user_00278</t>
+          <t>user_00285</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -11232,12 +11232,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>user_00300</t>
+          <t>user_00307</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>user_00278</t>
+          <t>user_00285</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -11265,12 +11265,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>user_00300</t>
+          <t>user_00307</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>user_00278</t>
+          <t>user_00285</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -11299,12 +11299,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>user_00300</t>
+          <t>user_00307</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>user_00278</t>
+          <t>user_00285</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -11332,12 +11332,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>user_00300</t>
+          <t>user_00307</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>user_00278</t>
+          <t>user_00285</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -11364,12 +11364,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>user_00300</t>
+          <t>user_00307</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>user_00278</t>
+          <t>user_00285</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -11396,12 +11396,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>user_00300</t>
+          <t>user_00307</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>user_00278</t>
+          <t>user_00285</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -11428,12 +11428,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>user_00300</t>
+          <t>user_00307</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>user_00278</t>
+          <t>user_00285</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -11460,12 +11460,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>user_00300</t>
+          <t>user_00307</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>user_00278</t>
+          <t>user_00285</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -11493,12 +11493,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>user_01329</t>
+          <t>user_01349</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>user_01265</t>
+          <t>user_01285</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -11509,7 +11509,7 @@
       <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="F324" t="n">
@@ -11531,12 +11531,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>user_01329</t>
+          <t>user_01349</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>user_01265</t>
+          <t>user_01285</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -11564,12 +11564,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>user_01329</t>
+          <t>user_01349</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>user_01265</t>
+          <t>user_01285</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -11597,12 +11597,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>user_01329</t>
+          <t>user_01349</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>user_01265</t>
+          <t>user_01285</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -11629,12 +11629,12 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>user_01329</t>
+          <t>user_01349</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>user_01265</t>
+          <t>user_01285</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -11661,12 +11661,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>user_01329</t>
+          <t>user_01349</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>user_01265</t>
+          <t>user_01285</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -11694,12 +11694,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>user_01329</t>
+          <t>user_01349</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>user_01265</t>
+          <t>user_01285</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -11726,12 +11726,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>user_01329</t>
+          <t>user_01349</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>user_01265</t>
+          <t>user_01285</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -11758,12 +11758,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>user_01329</t>
+          <t>user_01349</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>user_01265</t>
+          <t>user_01285</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -11791,12 +11791,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>user_01329</t>
+          <t>user_01349</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>user_01265</t>
+          <t>user_01285</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -11824,12 +11824,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>user_01329</t>
+          <t>user_01349</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>user_01265</t>
+          <t>user_01285</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -11856,12 +11856,12 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>user_01329</t>
+          <t>user_01349</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>user_01265</t>
+          <t>user_01285</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -11893,12 +11893,12 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>user_01329</t>
+          <t>user_01349</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>user_01265</t>
+          <t>user_01285</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -11926,12 +11926,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>user_01329</t>
+          <t>user_01349</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>user_01265</t>
+          <t>user_01285</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -11958,12 +11958,12 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>user_01329</t>
+          <t>user_01349</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>user_01265</t>
+          <t>user_01285</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -11990,12 +11990,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>user_01329</t>
+          <t>user_01349</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>user_01265</t>
+          <t>user_01285</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -12026,12 +12026,12 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>user_01329</t>
+          <t>user_01349</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>user_01265</t>
+          <t>user_01285</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -12059,12 +12059,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>user_01329</t>
+          <t>user_01349</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>user_01265</t>
+          <t>user_01285</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -12092,12 +12092,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>user_01329</t>
+          <t>user_01349</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>user_01265</t>
+          <t>user_01285</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -12126,12 +12126,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>user_01329</t>
+          <t>user_01349</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>user_01265</t>
+          <t>user_01285</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -12159,12 +12159,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>user_01329</t>
+          <t>user_01349</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>user_01265</t>
+          <t>user_01285</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -12191,12 +12191,12 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>user_01070</t>
+          <t>user_01085</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>user_02745</t>
+          <t>user_02806</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -12207,7 +12207,7 @@
       <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>user_02393</t>
+          <t>user_02435</t>
         </is>
       </c>
       <c r="F345" t="inlineStr"/>
@@ -12227,12 +12227,12 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>user_01070</t>
+          <t>user_01085</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>user_02745</t>
+          <t>user_02806</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -12259,12 +12259,12 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>user_01070</t>
+          <t>user_01085</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>user_02745</t>
+          <t>user_02806</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -12291,12 +12291,12 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>user_01070</t>
+          <t>user_01085</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>user_02745</t>
+          <t>user_02806</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -12323,12 +12323,12 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>user_01070</t>
+          <t>user_01085</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>user_02745</t>
+          <t>user_02806</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -12355,12 +12355,12 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>user_01070</t>
+          <t>user_01085</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>user_02745</t>
+          <t>user_02806</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -12387,12 +12387,12 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>user_01070</t>
+          <t>user_01085</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>user_02745</t>
+          <t>user_02806</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -12419,12 +12419,12 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>user_01070</t>
+          <t>user_01085</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>user_02745</t>
+          <t>user_02806</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -12452,12 +12452,12 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>user_01070</t>
+          <t>user_01085</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>user_02745</t>
+          <t>user_02806</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -12484,12 +12484,12 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>user_01070</t>
+          <t>user_01085</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>user_02745</t>
+          <t>user_02806</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -12516,12 +12516,12 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>user_01070</t>
+          <t>user_01085</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>user_02745</t>
+          <t>user_02806</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -12548,12 +12548,12 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>user_01070</t>
+          <t>user_01085</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>user_02745</t>
+          <t>user_02806</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -12580,12 +12580,12 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>user_01070</t>
+          <t>user_01085</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>user_02745</t>
+          <t>user_02806</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -12612,12 +12612,12 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>user_01070</t>
+          <t>user_01085</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>user_02745</t>
+          <t>user_02806</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -12644,12 +12644,12 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>user_01070</t>
+          <t>user_01085</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>user_02745</t>
+          <t>user_02806</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -12676,12 +12676,12 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>user_01070</t>
+          <t>user_01085</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>user_02745</t>
+          <t>user_02806</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -12708,12 +12708,12 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>user_01070</t>
+          <t>user_01085</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>user_02745</t>
+          <t>user_02806</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -12740,12 +12740,12 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>user_01070</t>
+          <t>user_01085</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>user_02745</t>
+          <t>user_02806</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -12774,12 +12774,12 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>user_01070</t>
+          <t>user_01085</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>user_02745</t>
+          <t>user_02806</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -12806,12 +12806,12 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>user_01070</t>
+          <t>user_01085</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>user_02745</t>
+          <t>user_02806</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -12840,12 +12840,12 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>user_01070</t>
+          <t>user_01085</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>user_02745</t>
+          <t>user_02806</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -12872,12 +12872,12 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>user_00379</t>
+          <t>user_00387</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -12911,12 +12911,12 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>user_00379</t>
+          <t>user_00387</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -12950,12 +12950,12 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>user_00379</t>
+          <t>user_00387</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -12999,12 +12999,12 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>user_00379</t>
+          <t>user_00387</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -13049,12 +13049,12 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>user_00379</t>
+          <t>user_00387</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -13091,12 +13091,12 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>user_00379</t>
+          <t>user_00387</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -13140,12 +13140,12 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>user_00379</t>
+          <t>user_00387</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -13180,12 +13180,12 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>user_00379</t>
+          <t>user_00387</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -13213,12 +13213,12 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>user_00379</t>
+          <t>user_00387</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -13246,12 +13246,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>user_00379</t>
+          <t>user_00387</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -13279,12 +13279,12 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>user_00379</t>
+          <t>user_00387</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -13311,12 +13311,12 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>user_00379</t>
+          <t>user_00387</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -13346,12 +13346,12 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>user_00379</t>
+          <t>user_00387</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -13378,12 +13378,12 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>user_00379</t>
+          <t>user_00387</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -13410,12 +13410,12 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>user_00379</t>
+          <t>user_00387</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -13442,12 +13442,12 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>user_00379</t>
+          <t>user_00387</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -13474,12 +13474,12 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>user_00379</t>
+          <t>user_00387</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -13507,12 +13507,12 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>user_00379</t>
+          <t>user_00387</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -13540,12 +13540,12 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>user_00379</t>
+          <t>user_00387</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -13572,12 +13572,12 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>user_00379</t>
+          <t>user_00387</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -13604,12 +13604,12 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>user_00379</t>
+          <t>user_00387</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -13636,12 +13636,12 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>user_00379</t>
+          <t>user_00387</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -13668,12 +13668,12 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>user_00379</t>
+          <t>user_00387</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -13702,12 +13702,12 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>user_00379</t>
+          <t>user_00387</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -13735,12 +13735,12 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>user_00379</t>
+          <t>user_00387</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -13767,12 +13767,12 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>user_00379</t>
+          <t>user_00387</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -13799,12 +13799,12 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>user_00379</t>
+          <t>user_00387</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -13832,12 +13832,12 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>user_01126</t>
+          <t>user_01145</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>user_02772</t>
+          <t>user_02835</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -13848,7 +13848,7 @@
       <c r="D393" t="inlineStr"/>
       <c r="E393" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="F393" t="n">
@@ -13870,12 +13870,12 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>user_02965</t>
+          <t>user_03045</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>user_00437</t>
+          <t>user_00445</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -13886,7 +13886,7 @@
       <c r="D394" t="inlineStr"/>
       <c r="E394" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="F394" t="n">
@@ -13908,12 +13908,12 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>user_02965</t>
+          <t>user_03045</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>user_00437</t>
+          <t>user_00445</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -13941,12 +13941,12 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>user_02965</t>
+          <t>user_03045</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>user_00437</t>
+          <t>user_00445</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -13974,12 +13974,12 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>user_02965</t>
+          <t>user_03045</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>user_00437</t>
+          <t>user_00445</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -14007,12 +14007,12 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>user_02965</t>
+          <t>user_03045</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>user_00437</t>
+          <t>user_00445</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -14040,12 +14040,12 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>user_02965</t>
+          <t>user_03045</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>user_00437</t>
+          <t>user_00445</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -14073,12 +14073,12 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>user_02965</t>
+          <t>user_03045</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>user_00437</t>
+          <t>user_00445</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -14111,12 +14111,12 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>user_02965</t>
+          <t>user_03045</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>user_00437</t>
+          <t>user_00445</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -14147,12 +14147,12 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>user_02965</t>
+          <t>user_03045</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>user_00437</t>
+          <t>user_00445</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -14181,12 +14181,12 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>user_02965</t>
+          <t>user_03045</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>user_00437</t>
+          <t>user_00445</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -14214,12 +14214,12 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>user_02965</t>
+          <t>user_03045</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>user_00437</t>
+          <t>user_00445</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -14247,12 +14247,12 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>user_02965</t>
+          <t>user_03045</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>user_00437</t>
+          <t>user_00445</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -14279,12 +14279,12 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>user_02965</t>
+          <t>user_03045</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>user_00437</t>
+          <t>user_00445</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -14311,12 +14311,12 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>user_02965</t>
+          <t>user_03045</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>user_00437</t>
+          <t>user_00445</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -14343,12 +14343,12 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>user_02965</t>
+          <t>user_03045</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>user_00437</t>
+          <t>user_00445</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -14375,12 +14375,12 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>user_02965</t>
+          <t>user_03045</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>user_00437</t>
+          <t>user_00445</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -14407,12 +14407,12 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>user_02965</t>
+          <t>user_03045</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>user_00437</t>
+          <t>user_00445</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -14440,12 +14440,12 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>user_01189</t>
+          <t>user_01208</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>user_02525</t>
+          <t>user_02576</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -14456,7 +14456,7 @@
       <c r="D411" t="inlineStr"/>
       <c r="E411" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -14479,12 +14479,12 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>user_01189</t>
+          <t>user_01208</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>user_02525</t>
+          <t>user_02576</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -14511,12 +14511,12 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>user_01189</t>
+          <t>user_01208</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>user_02525</t>
+          <t>user_02576</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -14543,12 +14543,12 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>user_01189</t>
+          <t>user_01208</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>user_02525</t>
+          <t>user_02576</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -14578,12 +14578,12 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>user_01189</t>
+          <t>user_01208</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>user_02525</t>
+          <t>user_02576</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -14610,12 +14610,12 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>user_01189</t>
+          <t>user_01208</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>user_02525</t>
+          <t>user_02576</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -14645,12 +14645,12 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>user_01189</t>
+          <t>user_01208</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>user_02525</t>
+          <t>user_02576</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -14677,12 +14677,12 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>user_01189</t>
+          <t>user_01208</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>user_02525</t>
+          <t>user_02576</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -14709,12 +14709,12 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>user_01189</t>
+          <t>user_01208</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>user_02525</t>
+          <t>user_02576</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -14742,12 +14742,12 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>user_01189</t>
+          <t>user_01208</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>user_02525</t>
+          <t>user_02576</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -14774,12 +14774,12 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>user_01189</t>
+          <t>user_01208</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>user_02525</t>
+          <t>user_02576</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -14807,12 +14807,12 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>user_01189</t>
+          <t>user_01208</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>user_02525</t>
+          <t>user_02576</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -14839,12 +14839,12 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>user_01189</t>
+          <t>user_01208</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>user_02525</t>
+          <t>user_02576</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -14871,12 +14871,12 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>user_01189</t>
+          <t>user_01208</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>user_02525</t>
+          <t>user_02576</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -14906,12 +14906,12 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>user_01189</t>
+          <t>user_01208</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>user_02525</t>
+          <t>user_02576</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -14938,12 +14938,12 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>user_01189</t>
+          <t>user_01208</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>user_02525</t>
+          <t>user_02576</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -14972,12 +14972,12 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>user_01189</t>
+          <t>user_01208</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>user_02525</t>
+          <t>user_02576</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -15005,12 +15005,12 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>user_01189</t>
+          <t>user_01208</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>user_02525</t>
+          <t>user_02576</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -15037,12 +15037,12 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>user_01189</t>
+          <t>user_01208</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>user_02525</t>
+          <t>user_02576</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -15069,12 +15069,12 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>user_01189</t>
+          <t>user_01208</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>user_02525</t>
+          <t>user_02576</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -15101,12 +15101,12 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>user_01189</t>
+          <t>user_01208</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>user_02525</t>
+          <t>user_02576</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -15133,12 +15133,12 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>user_01189</t>
+          <t>user_01208</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>user_02525</t>
+          <t>user_02576</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -15165,12 +15165,12 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>user_00380</t>
+          <t>user_00388</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>user_00382</t>
+          <t>user_00390</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -15181,7 +15181,7 @@
       <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="F433" t="n">
@@ -15206,12 +15206,12 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>user_00380</t>
+          <t>user_00388</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>user_00382</t>
+          <t>user_00390</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -15239,12 +15239,12 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>user_00380</t>
+          <t>user_00388</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>user_00382</t>
+          <t>user_00390</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -15275,12 +15275,12 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>user_00380</t>
+          <t>user_00388</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>user_00382</t>
+          <t>user_00390</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -15318,12 +15318,12 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>user_00380</t>
+          <t>user_00388</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>user_00382</t>
+          <t>user_00390</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -15354,12 +15354,12 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>user_00380</t>
+          <t>user_00388</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>user_00382</t>
+          <t>user_00390</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -15387,12 +15387,12 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>user_00380</t>
+          <t>user_00388</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>user_00382</t>
+          <t>user_00390</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -15421,12 +15421,12 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>user_00380</t>
+          <t>user_00388</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>user_00382</t>
+          <t>user_00390</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -15454,12 +15454,12 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>user_00380</t>
+          <t>user_00388</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>user_00382</t>
+          <t>user_00390</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -15488,12 +15488,12 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>user_00380</t>
+          <t>user_00388</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>user_00382</t>
+          <t>user_00390</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -15521,12 +15521,12 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>user_00380</t>
+          <t>user_00388</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>user_00382</t>
+          <t>user_00390</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -15554,12 +15554,12 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>user_00380</t>
+          <t>user_00388</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>user_00382</t>
+          <t>user_00390</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -15589,12 +15589,12 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>user_00380</t>
+          <t>user_00388</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>user_00382</t>
+          <t>user_00390</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -15624,12 +15624,12 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>user_00380</t>
+          <t>user_00388</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>user_00382</t>
+          <t>user_00390</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -15656,12 +15656,12 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>user_00380</t>
+          <t>user_00388</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>user_00382</t>
+          <t>user_00390</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -15689,12 +15689,12 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>user_00380</t>
+          <t>user_00388</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>user_00382</t>
+          <t>user_00390</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -15722,12 +15722,12 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>user_00380</t>
+          <t>user_00388</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>user_00382</t>
+          <t>user_00390</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -15756,12 +15756,12 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>user_00380</t>
+          <t>user_00388</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>user_00382</t>
+          <t>user_00390</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -15790,12 +15790,12 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>user_00380</t>
+          <t>user_00388</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>user_00382</t>
+          <t>user_00390</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -15823,12 +15823,12 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>user_02970</t>
+          <t>user_03050</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>user_01170</t>
+          <t>user_01189</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -15839,7 +15839,7 @@
       <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="F452" t="n">
@@ -15861,12 +15861,12 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>user_02970</t>
+          <t>user_03050</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>user_01170</t>
+          <t>user_01189</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -15893,12 +15893,12 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>user_02970</t>
+          <t>user_03050</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>user_01170</t>
+          <t>user_01189</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -15925,12 +15925,12 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>user_02970</t>
+          <t>user_03050</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>user_01170</t>
+          <t>user_01189</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -15958,12 +15958,12 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>user_02970</t>
+          <t>user_03050</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>user_01170</t>
+          <t>user_01189</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -15990,12 +15990,12 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>user_02970</t>
+          <t>user_03050</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>user_01170</t>
+          <t>user_01189</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -16023,12 +16023,12 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>user_02970</t>
+          <t>user_03050</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>user_01170</t>
+          <t>user_01189</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -16055,12 +16055,12 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>user_02970</t>
+          <t>user_03050</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>user_01170</t>
+          <t>user_01189</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -16087,12 +16087,12 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>user_02970</t>
+          <t>user_03050</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>user_01170</t>
+          <t>user_01189</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -16119,12 +16119,12 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>user_02970</t>
+          <t>user_03050</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>user_01170</t>
+          <t>user_01189</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -16151,12 +16151,12 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>user_02970</t>
+          <t>user_03050</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>user_01170</t>
+          <t>user_01189</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -16183,12 +16183,12 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>user_02970</t>
+          <t>user_03050</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>user_01170</t>
+          <t>user_01189</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -16216,12 +16216,12 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>user_02970</t>
+          <t>user_03050</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>user_01170</t>
+          <t>user_01189</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -16248,12 +16248,12 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>user_02970</t>
+          <t>user_03050</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>user_01170</t>
+          <t>user_01189</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -16280,12 +16280,12 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>user_02970</t>
+          <t>user_03050</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>user_01170</t>
+          <t>user_01189</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -16312,12 +16312,12 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>user_02970</t>
+          <t>user_03050</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>user_01170</t>
+          <t>user_01189</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -16344,12 +16344,12 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>user_02970</t>
+          <t>user_03050</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>user_01170</t>
+          <t>user_01189</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -16376,12 +16376,12 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>user_02970</t>
+          <t>user_03050</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>user_01170</t>
+          <t>user_01189</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -16408,12 +16408,12 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>user_02970</t>
+          <t>user_03050</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>user_01170</t>
+          <t>user_01189</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -16441,12 +16441,12 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>user_02970</t>
+          <t>user_03050</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>user_01170</t>
+          <t>user_01189</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -16473,12 +16473,12 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>user_02970</t>
+          <t>user_03050</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>user_01170</t>
+          <t>user_01189</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -16509,12 +16509,12 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>user_00457</t>
+          <t>user_00465</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>user_00458</t>
+          <t>user_00466</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -16525,7 +16525,7 @@
       <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="F473" t="n">
@@ -16547,12 +16547,12 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>user_01576</t>
+          <t>user_01597</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>user_01635</t>
+          <t>user_01656</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -16563,7 +16563,7 @@
       <c r="D474" t="inlineStr"/>
       <c r="E474" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="F474" t="n">
@@ -16588,12 +16588,12 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>user_01576</t>
+          <t>user_01597</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>user_01635</t>
+          <t>user_01656</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -16620,12 +16620,12 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>user_01576</t>
+          <t>user_01597</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>user_01635</t>
+          <t>user_01656</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -16653,12 +16653,12 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>user_01576</t>
+          <t>user_01597</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>user_01635</t>
+          <t>user_01656</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -16686,12 +16686,12 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>user_01576</t>
+          <t>user_01597</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>user_01635</t>
+          <t>user_01656</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -16719,12 +16719,12 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>user_01576</t>
+          <t>user_01597</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>user_01635</t>
+          <t>user_01656</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -16751,12 +16751,12 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>user_01576</t>
+          <t>user_01597</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>user_01635</t>
+          <t>user_01656</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -16785,12 +16785,12 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>user_01576</t>
+          <t>user_01597</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>user_01635</t>
+          <t>user_01656</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -16817,12 +16817,12 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>user_01576</t>
+          <t>user_01597</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>user_01635</t>
+          <t>user_01656</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -16850,12 +16850,12 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>user_01576</t>
+          <t>user_01597</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>user_01635</t>
+          <t>user_01656</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -16882,12 +16882,12 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>user_01576</t>
+          <t>user_01597</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>user_01635</t>
+          <t>user_01656</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -16915,12 +16915,12 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>user_01576</t>
+          <t>user_01597</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>user_01635</t>
+          <t>user_01656</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -16948,12 +16948,12 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>user_01576</t>
+          <t>user_01597</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>user_01635</t>
+          <t>user_01656</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -16982,12 +16982,12 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>user_01576</t>
+          <t>user_01597</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>user_01635</t>
+          <t>user_01656</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -17014,12 +17014,12 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>user_01576</t>
+          <t>user_01597</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>user_01635</t>
+          <t>user_01656</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -17047,12 +17047,12 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>user_01576</t>
+          <t>user_01597</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>user_01635</t>
+          <t>user_01656</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -17079,12 +17079,12 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>user_01072</t>
+          <t>user_01087</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>user_01104</t>
+          <t>user_01120</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -17095,7 +17095,7 @@
       <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="F490" t="n">
@@ -17117,12 +17117,12 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>user_00301</t>
+          <t>user_00308</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>user_02279</t>
+          <t>user_02310</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -17133,7 +17133,7 @@
       <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="F491" t="n">
@@ -17155,12 +17155,12 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>user_00301</t>
+          <t>user_00308</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>user_02279</t>
+          <t>user_02310</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -17187,12 +17187,12 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>user_00301</t>
+          <t>user_00308</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>user_02279</t>
+          <t>user_02310</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -17219,12 +17219,12 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>user_00301</t>
+          <t>user_00308</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>user_02279</t>
+          <t>user_02310</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -17251,12 +17251,12 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>user_00301</t>
+          <t>user_00308</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>user_02279</t>
+          <t>user_02310</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -17283,12 +17283,12 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>user_00301</t>
+          <t>user_00308</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>user_02279</t>
+          <t>user_02310</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -17316,12 +17316,12 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>user_00301</t>
+          <t>user_00308</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>user_02279</t>
+          <t>user_02310</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -17348,12 +17348,12 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>user_00301</t>
+          <t>user_00308</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>user_02279</t>
+          <t>user_02310</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -17381,12 +17381,12 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>user_00301</t>
+          <t>user_00308</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>user_02279</t>
+          <t>user_02310</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -17414,12 +17414,12 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>user_00301</t>
+          <t>user_00308</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>user_02279</t>
+          <t>user_02310</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -17446,12 +17446,12 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>user_00301</t>
+          <t>user_00308</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>user_02279</t>
+          <t>user_02310</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -17479,12 +17479,12 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>user_00301</t>
+          <t>user_00308</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>user_02279</t>
+          <t>user_02310</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -17513,12 +17513,12 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>user_00301</t>
+          <t>user_00308</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>user_02279</t>
+          <t>user_02310</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -17545,12 +17545,12 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>user_00301</t>
+          <t>user_00308</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>user_02279</t>
+          <t>user_02310</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -17578,12 +17578,12 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>user_00301</t>
+          <t>user_00308</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>user_02279</t>
+          <t>user_02310</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -17610,12 +17610,12 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>user_00301</t>
+          <t>user_00308</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>user_02279</t>
+          <t>user_02310</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -17642,12 +17642,12 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>user_00301</t>
+          <t>user_00308</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>user_02279</t>
+          <t>user_02310</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -17675,12 +17675,12 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>user_00301</t>
+          <t>user_00308</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>user_02279</t>
+          <t>user_02310</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -17707,12 +17707,12 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>user_00301</t>
+          <t>user_00308</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>user_02279</t>
+          <t>user_02310</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -17740,12 +17740,12 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>user_00301</t>
+          <t>user_00308</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>user_02279</t>
+          <t>user_02310</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -17772,12 +17772,12 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>user_00301</t>
+          <t>user_00308</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>user_02279</t>
+          <t>user_02310</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -17804,12 +17804,12 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>user_02414</t>
+          <t>user_02458</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>user_02407</t>
+          <t>user_02451</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -17820,7 +17820,7 @@
       <c r="D512" t="inlineStr"/>
       <c r="E512" t="inlineStr">
         <is>
-          <t>user_00452</t>
+          <t>user_00460</t>
         </is>
       </c>
       <c r="F512" t="n">
@@ -17843,12 +17843,12 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>user_00853</t>
+          <t>user_00866</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>user_02407</t>
+          <t>user_02451</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -17876,12 +17876,12 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>user_00853</t>
+          <t>user_00866</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>user_02407</t>
+          <t>user_02451</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -17910,12 +17910,12 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>user_00853</t>
+          <t>user_00866</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>user_02407</t>
+          <t>user_02451</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -17942,12 +17942,12 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>user_00853</t>
+          <t>user_00866</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>user_02407</t>
+          <t>user_02451</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -17976,12 +17976,12 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>user_00853</t>
+          <t>user_00866</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>user_02407</t>
+          <t>user_02451</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -18008,12 +18008,12 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>user_00853</t>
+          <t>user_00866</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>user_02407</t>
+          <t>user_02451</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -18040,12 +18040,12 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>user_00853</t>
+          <t>user_00866</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>user_02407</t>
+          <t>user_02451</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -18075,12 +18075,12 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>user_00853</t>
+          <t>user_00866</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>user_02407</t>
+          <t>user_02451</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -18107,12 +18107,12 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>user_00853</t>
+          <t>user_00866</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>user_02407</t>
+          <t>user_02451</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -18139,12 +18139,12 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>user_00853</t>
+          <t>user_00866</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>user_02407</t>
+          <t>user_02451</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -18171,12 +18171,12 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>user_00853</t>
+          <t>user_00866</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>user_02407</t>
+          <t>user_02451</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">

--- a/#BillsMafia_anonymized.xlsx
+++ b/#BillsMafia_anonymized.xlsx
@@ -519,7 +519,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12904,7 +12904,7 @@
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12943,7 +12943,7 @@
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12992,7 +12992,7 @@
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13042,7 +13042,7 @@
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13084,7 +13084,7 @@
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13173,7 +13173,7 @@
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
